--- a/materials/Экспертные_ожидания_Евы_по_контрастным_анкетам.xlsx
+++ b/materials/Экспертные_ожидания_Евы_по_контрастным_анкетам.xlsx
@@ -564,7 +564,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -1134,7 +1134,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="85" customWidth="1" min="2" max="2"/>
